--- a/artfynd/A 36220-2023 artfynd.xlsx
+++ b/artfynd/A 36220-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36220-2023 artfynd.xlsx
+++ b/artfynd/A 36220-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111739313</v>
+        <v>111739310</v>
       </c>
       <c r="B2" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574025</v>
+        <v>574040</v>
       </c>
       <c r="R2" t="n">
-        <v>7172443</v>
+        <v>7172445</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111739306</v>
+        <v>111739313</v>
       </c>
       <c r="B3" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573906</v>
+        <v>574025</v>
       </c>
       <c r="R3" t="n">
-        <v>7172521</v>
+        <v>7172443</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111739307</v>
+        <v>111739317</v>
       </c>
       <c r="B4" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,43 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573961</v>
+        <v>573912</v>
       </c>
       <c r="R4" t="n">
-        <v>7172501</v>
+        <v>7172648</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111739317</v>
+        <v>111739311</v>
       </c>
       <c r="B5" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573912</v>
+        <v>574012</v>
       </c>
       <c r="R5" t="n">
-        <v>7172648</v>
+        <v>7172473</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111739311</v>
+        <v>111739303</v>
       </c>
       <c r="B6" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574012</v>
+        <v>574047</v>
       </c>
       <c r="R6" t="n">
-        <v>7172473</v>
+        <v>7172508</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111739315</v>
+        <v>111739316</v>
       </c>
       <c r="B7" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111739316</v>
+        <v>111739315</v>
       </c>
       <c r="B8" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1403,50 +1354,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111739309</v>
+        <v>111739305</v>
       </c>
       <c r="B9" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bräntkullarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574011</v>
+        <v>574040</v>
       </c>
       <c r="R9" t="n">
-        <v>7172434</v>
+        <v>7172430</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1502,6 +1453,533 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111739306</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573906</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7172521</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111739308</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573904</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7172486</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111739312</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574055</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7172474</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111739307</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573960</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7172502</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111739309</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bräntkullarna, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574011</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7172434</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
